--- a/资产列表.xlsx
+++ b/资产列表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3500" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3500" uniqueCount="547">
   <si>
     <t>IP地址</t>
   </si>
@@ -1623,6 +1623,9 @@
   </si>
   <si>
     <t>10.247.205.114</t>
+  </si>
+  <si>
+    <t>子组名12312312312312314444444444444444444444444444444444444444444444442，哈哈哈</t>
   </si>
   <si>
     <t>10.225.53.62</t>
@@ -13799,12 +13802,12 @@
         <v>12</v>
       </c>
       <c r="G486" t="s">
-        <v>13</v>
+        <v>531</v>
       </c>
     </row>
     <row r="487" spans="1:7">
       <c r="A487" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B487" t="s">
         <v>339</v>
@@ -13827,7 +13830,7 @@
     </row>
     <row r="488" spans="1:7">
       <c r="A488" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B488" t="s">
         <v>317</v>
@@ -13850,7 +13853,7 @@
     </row>
     <row r="489" spans="1:7">
       <c r="A489" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B489" t="s">
         <v>317</v>
@@ -13873,7 +13876,7 @@
     </row>
     <row r="490" spans="1:7">
       <c r="A490" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B490" t="s">
         <v>393</v>
@@ -13896,7 +13899,7 @@
     </row>
     <row r="491" spans="1:7">
       <c r="A491" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B491" t="s">
         <v>375</v>
@@ -13919,7 +13922,7 @@
     </row>
     <row r="492" spans="1:7">
       <c r="A492" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B492" t="s">
         <v>321</v>
@@ -13942,7 +13945,7 @@
     </row>
     <row r="493" spans="1:7">
       <c r="A493" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B493" t="s">
         <v>337</v>
@@ -13965,7 +13968,7 @@
     </row>
     <row r="494" spans="1:7">
       <c r="A494" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B494" t="s">
         <v>325</v>
@@ -13988,7 +13991,7 @@
     </row>
     <row r="495" spans="1:7">
       <c r="A495" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B495" t="s">
         <v>325</v>
@@ -14011,7 +14014,7 @@
     </row>
     <row r="496" spans="1:7">
       <c r="A496" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B496" t="s">
         <v>319</v>
@@ -14034,7 +14037,7 @@
     </row>
     <row r="497" spans="1:7">
       <c r="A497" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B497" t="s">
         <v>325</v>
@@ -14057,7 +14060,7 @@
     </row>
     <row r="498" spans="1:7">
       <c r="A498" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B498" t="s">
         <v>395</v>
@@ -14080,7 +14083,7 @@
     </row>
     <row r="499" spans="1:7">
       <c r="A499" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B499" t="s">
         <v>366</v>
@@ -14103,7 +14106,7 @@
     </row>
     <row r="500" spans="1:7">
       <c r="A500" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B500" t="s">
         <v>8</v>
@@ -14126,7 +14129,7 @@
     </row>
     <row r="501" spans="1:7">
       <c r="A501" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B501" t="s">
         <v>482</v>
